--- a/2025-FLL-Qualifier-Tournaments.xlsx
+++ b/2025-FLL-Qualifier-Tournaments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github-projects\FLL-Season-and-Tournament-Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F28E80CE-93CD-48C4-9332-B20E908E8F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91BD3EC-59B1-40F3-823D-1C4E3D3DC6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{0852510A-0402-494B-87EA-4B91755641F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{0852510A-0402-494B-87EA-4B91755641F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="9" r:id="rId1"/>
@@ -7776,22 +7776,22 @@
         <v>219</v>
       </c>
       <c r="E15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K15" s="1">
         <v>0</v>
@@ -7806,7 +7806,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">

--- a/2025-FLL-Qualifier-Tournaments.xlsx
+++ b/2025-FLL-Qualifier-Tournaments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github-projects\FLL-Season-and-Tournament-Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3F1EFAD-F5C7-4D18-B214-44811E7EAEF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{750699C5-1A14-4AED-AB3D-1354FF59F091}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{0852510A-0402-494B-87EA-4B91755641F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="3" xr2:uid="{0852510A-0402-494B-87EA-4B91755641F1}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="9" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2779" uniqueCount="1419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2335" uniqueCount="1217">
   <si>
     <t>Ribbons</t>
   </si>
@@ -3714,612 +3714,6 @@
   </si>
   <si>
     <t>Windmere Gate 2025 Unearthed Qualifier Tournament</t>
-  </si>
-  <si>
-    <t>Champ1</t>
-  </si>
-  <si>
-    <t>VADC 2025 Championship Division 1 Tournament</t>
-  </si>
-  <si>
-    <t>Champ2</t>
-  </si>
-  <si>
-    <t>VADC 2025 Championship Division 2 Tournament</t>
-  </si>
-  <si>
-    <t>Robellion</t>
-  </si>
-  <si>
-    <t>Lang Ly</t>
-  </si>
-  <si>
-    <t>Nova Labs</t>
-  </si>
-  <si>
-    <t>Greenbrier Panthers</t>
-  </si>
-  <si>
-    <t>Greenbrier Intermediate School</t>
-  </si>
-  <si>
-    <t>Victory Robotics</t>
-  </si>
-  <si>
-    <t>Joy Moller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Victory Elementary </t>
-  </si>
-  <si>
-    <t>Space Invaders</t>
-  </si>
-  <si>
-    <t>Josselyn Fountain</t>
-  </si>
-  <si>
-    <t>Chris Yung Elementary</t>
-  </si>
-  <si>
-    <t>In T.E.N.T.S.</t>
-  </si>
-  <si>
-    <t>Michael Hobbs</t>
-  </si>
-  <si>
-    <t>Hillsville Elementary</t>
-  </si>
-  <si>
-    <t>Glenkirk Golden Gears</t>
-  </si>
-  <si>
-    <t>Jennifer Oister</t>
-  </si>
-  <si>
-    <t>Glenkirk Elementary</t>
-  </si>
-  <si>
-    <t>8 Stars</t>
-  </si>
-  <si>
-    <t>Jennifer Roberts</t>
-  </si>
-  <si>
-    <t>Piney Branch Elementary School</t>
-  </si>
-  <si>
-    <t>The Sea Salters</t>
-  </si>
-  <si>
-    <t>Todd Hedrick</t>
-  </si>
-  <si>
-    <t>Hillsville Elementary School</t>
-  </si>
-  <si>
-    <t>Mighty Mount Vernon Mustangs</t>
-  </si>
-  <si>
-    <t>Mt. Vernon Elementary School</t>
-  </si>
-  <si>
-    <t>The Mini Jackets</t>
-  </si>
-  <si>
-    <t>Patrick Heath</t>
-  </si>
-  <si>
-    <t>Osbourn Park High School</t>
-  </si>
-  <si>
-    <t>The Wild Robots</t>
-  </si>
-  <si>
-    <t>Martha Wild</t>
-  </si>
-  <si>
-    <t>Greenfield Elementary</t>
-  </si>
-  <si>
-    <t>Marshall Eaglebots</t>
-  </si>
-  <si>
-    <t>Nick Simonetti</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marshall Elementary </t>
-  </si>
-  <si>
-    <t>Coding Cats</t>
-  </si>
-  <si>
-    <t>Ryan Daza</t>
-  </si>
-  <si>
-    <t>Capitol City Robotics</t>
-  </si>
-  <si>
-    <t>Excavating Gators</t>
-  </si>
-  <si>
-    <t>Kimberly Hundley</t>
-  </si>
-  <si>
-    <t>Gladesboro Elementary</t>
-  </si>
-  <si>
-    <t>The PHinders</t>
-  </si>
-  <si>
-    <t>Erika Crockett</t>
-  </si>
-  <si>
-    <t>Patrick Henry Elementary School</t>
-  </si>
-  <si>
-    <t>Beam Bots</t>
-  </si>
-  <si>
-    <t>Palani Annamalai</t>
-  </si>
-  <si>
-    <t>Fire Breathing Gummy Bears</t>
-  </si>
-  <si>
-    <t>Ian Armitage</t>
-  </si>
-  <si>
-    <t>St. Catherine's School</t>
-  </si>
-  <si>
-    <t>The Fried Eggs</t>
-  </si>
-  <si>
-    <t>Melonie Yielding</t>
-  </si>
-  <si>
-    <t>Innovation ES</t>
-  </si>
-  <si>
-    <t>Rhea Valley Dino Nuggets</t>
-  </si>
-  <si>
-    <t>Jeremiah Eskridge</t>
-  </si>
-  <si>
-    <t>Alvey Sun Droids</t>
-  </si>
-  <si>
-    <t>Deborah Tekampe</t>
-  </si>
-  <si>
-    <t>Alvey Elementary</t>
-  </si>
-  <si>
-    <t>Saints Robotics</t>
-  </si>
-  <si>
-    <t>Kay Ossio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">St. Stephen's and St. Agnes </t>
-  </si>
-  <si>
-    <t>Mechanical Cardinals</t>
-  </si>
-  <si>
-    <t>LEGOAT Legends</t>
-  </si>
-  <si>
-    <t>Erin Tarpley</t>
-  </si>
-  <si>
-    <t>Raiders of the Lost Spark</t>
-  </si>
-  <si>
-    <t>Alicia Simonds</t>
-  </si>
-  <si>
-    <t>Springwoods Elementary</t>
-  </si>
-  <si>
-    <t>RoboCougars</t>
-  </si>
-  <si>
-    <t>Rachael Rachau</t>
-  </si>
-  <si>
-    <t>Collegiate School</t>
-  </si>
-  <si>
-    <t>Indiana Janes</t>
-  </si>
-  <si>
-    <t>Bhavan N Pandya</t>
-  </si>
-  <si>
-    <t>Hillside Elementary</t>
-  </si>
-  <si>
-    <t>Robo Diggers</t>
-  </si>
-  <si>
-    <t>Bengalbots</t>
-  </si>
-  <si>
-    <t>Andrea Heithoff</t>
-  </si>
-  <si>
-    <t>Bancroft Elementary School</t>
-  </si>
-  <si>
-    <t>Robodragons</t>
-  </si>
-  <si>
-    <t>Patty Pippenger</t>
-  </si>
-  <si>
-    <t>NGES Lego Dragoneers</t>
-  </si>
-  <si>
-    <t>Erin Cummings</t>
-  </si>
-  <si>
-    <t>Nathanael Greene Elementary School</t>
-  </si>
-  <si>
-    <t>Curious Minds</t>
-  </si>
-  <si>
-    <t>Rohan Gupta</t>
-  </si>
-  <si>
-    <t>Cool Robot Bruh</t>
-  </si>
-  <si>
-    <t>Newsome Park Elementary School</t>
-  </si>
-  <si>
-    <t>Roar Bot 13</t>
-  </si>
-  <si>
-    <t>Carolyn Sandoval</t>
-  </si>
-  <si>
-    <t>Christ Chapel Academy</t>
-  </si>
-  <si>
-    <t>Mecha Masters</t>
-  </si>
-  <si>
-    <t>Ankur Mittal</t>
-  </si>
-  <si>
-    <t>Odin Wise</t>
-  </si>
-  <si>
-    <t>Chaos Seekers</t>
-  </si>
-  <si>
-    <t>Michelle Curtis</t>
-  </si>
-  <si>
-    <t>Miner Minions</t>
-  </si>
-  <si>
-    <t>JB Watkins Elementary</t>
-  </si>
-  <si>
-    <t>Scripted Builders</t>
-  </si>
-  <si>
-    <t>The Sandstorms</t>
-  </si>
-  <si>
-    <t>Erin Roche</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Bristow Run Elementary</t>
-  </si>
-  <si>
-    <t>Robo-Penguins</t>
-  </si>
-  <si>
-    <t>Doug Tempest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mary Munford </t>
-  </si>
-  <si>
-    <t>Kaechele Coyotes-Brickologists</t>
-  </si>
-  <si>
-    <t>Jay Harter</t>
-  </si>
-  <si>
-    <t>Kaechele Elementary School</t>
-  </si>
-  <si>
-    <t>Nebula Horizon</t>
-  </si>
-  <si>
-    <t>Devaki Venkataramanaiah</t>
-  </si>
-  <si>
-    <t>Oakhill</t>
-  </si>
-  <si>
-    <t>The Ancient UNCS</t>
-  </si>
-  <si>
-    <t>Srinivasalu Simini</t>
-  </si>
-  <si>
-    <t>Yantra Robotics Academy</t>
-  </si>
-  <si>
-    <t>Sigma7</t>
-  </si>
-  <si>
-    <t>Kalyan Lanka</t>
-  </si>
-  <si>
-    <t>McLean Robotics</t>
-  </si>
-  <si>
-    <t>Synergy</t>
-  </si>
-  <si>
-    <t>Christina Rodi</t>
-  </si>
-  <si>
-    <t>I4STEM</t>
-  </si>
-  <si>
-    <t>CYBORG CODERS</t>
-  </si>
-  <si>
-    <t>Jitendra Kumar</t>
-  </si>
-  <si>
-    <t>Carrie Matsko</t>
-  </si>
-  <si>
-    <t>Kalamoo Community Outreach</t>
-  </si>
-  <si>
-    <t>Treasure Trappers</t>
-  </si>
-  <si>
-    <t>Jennifer Payne</t>
-  </si>
-  <si>
-    <t>Salem Montessori</t>
-  </si>
-  <si>
-    <t>RoboDragons</t>
-  </si>
-  <si>
-    <t>Varun Aggarwal</t>
-  </si>
-  <si>
-    <t>Maybeury Mallards Challenge Team</t>
-  </si>
-  <si>
-    <t>Christina Robertson</t>
-  </si>
-  <si>
-    <t>Maybeury Elementary-HCPS</t>
-  </si>
-  <si>
-    <t>The Dirty Byrds</t>
-  </si>
-  <si>
-    <t>Zoe Parrish</t>
-  </si>
-  <si>
-    <t>Byrd Elementary School</t>
-  </si>
-  <si>
-    <t>Bionical Brains</t>
-  </si>
-  <si>
-    <t>Vishwas Setty</t>
-  </si>
-  <si>
-    <t>Eshkavaitors</t>
-  </si>
-  <si>
-    <t>Suman Sampath</t>
-  </si>
-  <si>
-    <t>McNair Upper Elementary</t>
-  </si>
-  <si>
-    <t>UNEARTHED TITANS</t>
-  </si>
-  <si>
-    <t>Chinna Obul R Kachana</t>
-  </si>
-  <si>
-    <t>Fossil Force</t>
-  </si>
-  <si>
-    <t>Absolute Zero</t>
-  </si>
-  <si>
-    <t>Tomb Raiders</t>
-  </si>
-  <si>
-    <t>Norfolk Collegiate O.A.K.S.</t>
-  </si>
-  <si>
-    <t>Techtonic Force</t>
-  </si>
-  <si>
-    <t>Blazing Torch</t>
-  </si>
-  <si>
-    <t>The Fragile Castdown</t>
-  </si>
-  <si>
-    <t>Notorious D.I.G. (Digging, Identifying, Grouping)</t>
-  </si>
-  <si>
-    <t>OLMC Yellow</t>
-  </si>
-  <si>
-    <t>MasterMinds</t>
-  </si>
-  <si>
-    <t>The Mountain Miners</t>
-  </si>
-  <si>
-    <t>The Ancient Chickens</t>
-  </si>
-  <si>
-    <t>Night Owls</t>
-  </si>
-  <si>
-    <t>roboFoxes</t>
-  </si>
-  <si>
-    <t>Blinged Out Bumblebees</t>
-  </si>
-  <si>
-    <t>OLMC Blue</t>
-  </si>
-  <si>
-    <t>The Lego My Eggo Cows</t>
-  </si>
-  <si>
-    <t>Ultrabots</t>
-  </si>
-  <si>
-    <t>Bobcat Builders</t>
-  </si>
-  <si>
-    <t>Pink Ladies</t>
-  </si>
-  <si>
-    <t>Red Saints</t>
-  </si>
-  <si>
-    <t>Next Level</t>
-  </si>
-  <si>
-    <t>Tech Turtles</t>
-  </si>
-  <si>
-    <t>Raiders</t>
-  </si>
-  <si>
-    <t>Amazing Samurai</t>
-  </si>
-  <si>
-    <t>Trailblazing Titans</t>
-  </si>
-  <si>
-    <t>~ Wild Spirits ~</t>
-  </si>
-  <si>
-    <t>Star City Tronics</t>
-  </si>
-  <si>
-    <t>Alpha Bots</t>
-  </si>
-  <si>
-    <t>Circuit Squirrels</t>
-  </si>
-  <si>
-    <t>Potomac PyRitz</t>
-  </si>
-  <si>
-    <t>Lego Legends</t>
-  </si>
-  <si>
-    <t>Supercharged</t>
-  </si>
-  <si>
-    <t>Limitless</t>
-  </si>
-  <si>
-    <t>Igniteovators</t>
-  </si>
-  <si>
-    <t>Lego Bros</t>
-  </si>
-  <si>
-    <t>Lego Warriors</t>
-  </si>
-  <si>
-    <t>Dolphin Dazzle</t>
-  </si>
-  <si>
-    <t>ITKAN-MASMinds</t>
-  </si>
-  <si>
-    <t>Garfield Lego Robotics</t>
-  </si>
-  <si>
-    <t>Dragons and Unicorns</t>
-  </si>
-  <si>
-    <t>Rainbow Radishes</t>
-  </si>
-  <si>
-    <t>Wired Dolphins</t>
-  </si>
-  <si>
-    <t>Robot Rebels- Skywalkers</t>
-  </si>
-  <si>
-    <t>Show of Hands</t>
-  </si>
-  <si>
-    <t>The Embers</t>
-  </si>
-  <si>
-    <t>Lego Legion 1</t>
-  </si>
-  <si>
-    <t>Andromeda</t>
-  </si>
-  <si>
-    <t>The Masterpiece Academy</t>
-  </si>
-  <si>
-    <t>Dime Dinos</t>
-  </si>
-  <si>
-    <t>M squared</t>
-  </si>
-  <si>
-    <t>The Lava Chickens</t>
-  </si>
-  <si>
-    <t>Tech Titans</t>
-  </si>
-  <si>
-    <t>Adventurous Armadillos</t>
-  </si>
-  <si>
-    <t>PlasmaBots!</t>
-  </si>
-  <si>
-    <t>Mechanical Minds</t>
-  </si>
-  <si>
-    <t>Team Maverick</t>
-  </si>
-  <si>
-    <t>Gryffin Gears</t>
-  </si>
-  <si>
-    <t>Block Buster</t>
-  </si>
-  <si>
-    <t>FOSSIL FINDERS</t>
   </si>
 </sst>
 </file>
@@ -5794,8 +5188,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6A06E95-68C8-4940-B680-2C0995F031C3}" name="DivTournamentList" displayName="DivTournamentList" ref="A1:M40" totalsRowShown="0">
-  <autoFilter ref="A1:M40" xr:uid="{B6A06E95-68C8-4940-B680-2C0995F031C3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{B6A06E95-68C8-4940-B680-2C0995F031C3}" name="DivTournamentList" displayName="DivTournamentList" ref="A1:M38" totalsRowShown="0">
+  <autoFilter ref="A1:M38" xr:uid="{B6A06E95-68C8-4940-B680-2C0995F031C3}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{13A1917A-5FA7-45FA-916C-27FE0F8E0A97}" name="Short Name"/>
     <tableColumn id="7" xr3:uid="{9239BE62-20DE-4C00-B4EA-0F023772BA66}" name="Long Name" dataDxfId="22"/>
@@ -5820,8 +5214,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5245E064-699F-4B50-AC64-10C5360A5DC3}" name="Assignments" displayName="Assignments" ref="A1:H531" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:H531" xr:uid="{5245E064-699F-4B50-AC64-10C5360A5DC3}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{5245E064-699F-4B50-AC64-10C5360A5DC3}" name="Assignments" displayName="Assignments" ref="A1:H418" totalsRowShown="0" dataDxfId="13">
+  <autoFilter ref="A1:H418" xr:uid="{5245E064-699F-4B50-AC64-10C5360A5DC3}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H389">
     <sortCondition ref="F1:F389"/>
   </sortState>
@@ -8538,7 +7932,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0B7B0F1-8C69-412F-8013-AD404FAFA062}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -10188,92 +9582,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1218</v>
-      </c>
-      <c r="C39" s="7">
-        <v>46032</v>
-      </c>
-      <c r="D39" t="s">
-        <v>23</v>
-      </c>
-      <c r="E39" t="str">
-        <f>DivTournamentList[[#This Row],[Short Name]]&amp;DivTournamentList[[#This Row],[Div]]</f>
-        <v>Champ1D1</v>
-      </c>
-      <c r="F39" t="str">
-        <f>"2025-vadc-fll-challenge-Unearthed-ojs-" &amp; DivTournamentList[[#This Row],[Helper]] &amp; ".xlsm"</f>
-        <v>2025-vadc-fll-challenge-Unearthed-ojs-Champ1D1.xlsm</v>
-      </c>
-      <c r="G39">
-        <v>3</v>
-      </c>
-      <c r="H39">
-        <v>3</v>
-      </c>
-      <c r="I39">
-        <v>3</v>
-      </c>
-      <c r="J39">
-        <v>3</v>
-      </c>
-      <c r="K39">
-        <v>3</v>
-      </c>
-      <c r="L39">
-        <v>0</v>
-      </c>
-      <c r="M39">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B40" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C40" s="7">
-        <v>46033</v>
-      </c>
-      <c r="D40" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" t="str">
-        <f>DivTournamentList[[#This Row],[Short Name]]&amp;DivTournamentList[[#This Row],[Div]]</f>
-        <v>Champ2D2</v>
-      </c>
-      <c r="F40" t="str">
-        <f>"2025-vadc-fll-challenge-Unearthed-ojs-" &amp; DivTournamentList[[#This Row],[Helper]] &amp; ".xlsm"</f>
-        <v>2025-vadc-fll-challenge-Unearthed-ojs-Champ2D2.xlsm</v>
-      </c>
-      <c r="G40">
-        <v>3</v>
-      </c>
-      <c r="H40">
-        <v>3</v>
-      </c>
-      <c r="I40">
-        <v>3</v>
-      </c>
-      <c r="J40">
-        <v>3</v>
-      </c>
-      <c r="K40">
-        <v>3</v>
-      </c>
-      <c r="L40">
-        <v>0</v>
-      </c>
-      <c r="M40">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10287,7 +9595,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F76FCFD-7913-48E7-8A1D-892F3A9B6B36}">
-  <dimension ref="A1:H531"/>
+  <dimension ref="A1:H418"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.85546875" bestFit="1" customWidth="1"/>
@@ -20092,2234 +19400,6 @@
         <v>3</v>
       </c>
       <c r="H418" s="3"/>
-    </row>
-    <row r="419" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A419" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B419" s="3">
-        <v>112</v>
-      </c>
-      <c r="C419" s="3" t="s">
-        <v>1221</v>
-      </c>
-      <c r="D419" s="3" t="s">
-        <v>1222</v>
-      </c>
-      <c r="E419" s="3" t="s">
-        <v>1223</v>
-      </c>
-      <c r="F419" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G419" s="3"/>
-      <c r="H419" s="3"/>
-    </row>
-    <row r="420" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A420" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B420" s="3">
-        <v>9021</v>
-      </c>
-      <c r="C420" s="3" t="s">
-        <v>1224</v>
-      </c>
-      <c r="D420" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="E420" s="3" t="s">
-        <v>1225</v>
-      </c>
-      <c r="F420" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G420" s="3"/>
-      <c r="H420" s="3"/>
-    </row>
-    <row r="421" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A421" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B421" s="3">
-        <v>10321</v>
-      </c>
-      <c r="C421" s="3" t="s">
-        <v>1226</v>
-      </c>
-      <c r="D421" s="3" t="s">
-        <v>1227</v>
-      </c>
-      <c r="E421" s="3" t="s">
-        <v>1228</v>
-      </c>
-      <c r="F421" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G421" s="3"/>
-      <c r="H421" s="3"/>
-    </row>
-    <row r="422" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A422" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B422" s="3">
-        <v>20349</v>
-      </c>
-      <c r="C422" s="3" t="s">
-        <v>1229</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>1230</v>
-      </c>
-      <c r="E422" s="3" t="s">
-        <v>1231</v>
-      </c>
-      <c r="F422" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G422" s="3"/>
-      <c r="H422" s="3"/>
-    </row>
-    <row r="423" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A423" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B423" s="3">
-        <v>23372</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>1232</v>
-      </c>
-      <c r="D423" s="3" t="s">
-        <v>1233</v>
-      </c>
-      <c r="E423" s="3" t="s">
-        <v>1234</v>
-      </c>
-      <c r="F423" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G423" s="3"/>
-      <c r="H423" s="3"/>
-    </row>
-    <row r="424" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A424" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B424" s="3">
-        <v>24317</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>1235</v>
-      </c>
-      <c r="D424" s="3" t="s">
-        <v>1236</v>
-      </c>
-      <c r="E424" s="3" t="s">
-        <v>1237</v>
-      </c>
-      <c r="F424" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G424" s="3"/>
-      <c r="H424" s="3"/>
-    </row>
-    <row r="425" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A425" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B425" s="3">
-        <v>27239</v>
-      </c>
-      <c r="C425" s="3" t="s">
-        <v>1238</v>
-      </c>
-      <c r="D425" s="3" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E425" s="3" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F425" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G425" s="3"/>
-      <c r="H425" s="3"/>
-    </row>
-    <row r="426" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A426" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B426" s="3">
-        <v>32350</v>
-      </c>
-      <c r="C426" s="3" t="s">
-        <v>1241</v>
-      </c>
-      <c r="D426" s="3" t="s">
-        <v>1242</v>
-      </c>
-      <c r="E426" s="3" t="s">
-        <v>1243</v>
-      </c>
-      <c r="F426" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G426" s="3"/>
-      <c r="H426" s="3"/>
-    </row>
-    <row r="427" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A427" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B427" s="3">
-        <v>37683</v>
-      </c>
-      <c r="C427" s="3" t="s">
-        <v>1244</v>
-      </c>
-      <c r="D427" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E427" s="3" t="s">
-        <v>1245</v>
-      </c>
-      <c r="F427" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G427" s="3"/>
-      <c r="H427" s="3"/>
-    </row>
-    <row r="428" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A428" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B428" s="3">
-        <v>37711</v>
-      </c>
-      <c r="C428" s="3" t="s">
-        <v>1246</v>
-      </c>
-      <c r="D428" s="3" t="s">
-        <v>1247</v>
-      </c>
-      <c r="E428" s="3" t="s">
-        <v>1248</v>
-      </c>
-      <c r="F428" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G428" s="3"/>
-      <c r="H428" s="3"/>
-    </row>
-    <row r="429" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A429" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B429" s="3">
-        <v>38363</v>
-      </c>
-      <c r="C429" s="3" t="s">
-        <v>1249</v>
-      </c>
-      <c r="D429" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="E429" s="3" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F429" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G429" s="3"/>
-      <c r="H429" s="3"/>
-    </row>
-    <row r="430" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A430" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B430" s="3">
-        <v>39343</v>
-      </c>
-      <c r="C430" s="3" t="s">
-        <v>1252</v>
-      </c>
-      <c r="D430" s="3" t="s">
-        <v>1253</v>
-      </c>
-      <c r="E430" s="3" t="s">
-        <v>1254</v>
-      </c>
-      <c r="F430" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G430" s="3"/>
-      <c r="H430" s="3"/>
-    </row>
-    <row r="431" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A431" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B431" s="3">
-        <v>46457</v>
-      </c>
-      <c r="C431" s="3" t="s">
-        <v>1255</v>
-      </c>
-      <c r="D431" s="3" t="s">
-        <v>1256</v>
-      </c>
-      <c r="E431" s="3" t="s">
-        <v>1257</v>
-      </c>
-      <c r="F431" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G431" s="3"/>
-      <c r="H431" s="3"/>
-    </row>
-    <row r="432" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A432" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B432" s="3">
-        <v>51572</v>
-      </c>
-      <c r="C432" s="3" t="s">
-        <v>1258</v>
-      </c>
-      <c r="D432" s="3" t="s">
-        <v>1259</v>
-      </c>
-      <c r="E432" s="3" t="s">
-        <v>1260</v>
-      </c>
-      <c r="F432" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G432" s="3"/>
-      <c r="H432" s="3"/>
-    </row>
-    <row r="433" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A433" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B433" s="3">
-        <v>53121</v>
-      </c>
-      <c r="C433" s="3" t="s">
-        <v>1261</v>
-      </c>
-      <c r="D433" s="3" t="s">
-        <v>1262</v>
-      </c>
-      <c r="E433" s="3" t="s">
-        <v>1263</v>
-      </c>
-      <c r="F433" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G433" s="3"/>
-      <c r="H433" s="3"/>
-    </row>
-    <row r="434" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A434" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B434" s="3">
-        <v>53240</v>
-      </c>
-      <c r="C434" s="3" t="s">
-        <v>1264</v>
-      </c>
-      <c r="D434" s="3" t="s">
-        <v>1265</v>
-      </c>
-      <c r="E434" s="3"/>
-      <c r="F434" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G434" s="3"/>
-      <c r="H434" s="3"/>
-    </row>
-    <row r="435" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A435" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B435" s="3">
-        <v>55754</v>
-      </c>
-      <c r="C435" s="3" t="s">
-        <v>1266</v>
-      </c>
-      <c r="D435" s="3" t="s">
-        <v>1267</v>
-      </c>
-      <c r="E435" s="3" t="s">
-        <v>1268</v>
-      </c>
-      <c r="F435" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G435" s="3"/>
-      <c r="H435" s="3"/>
-    </row>
-    <row r="436" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A436" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B436" s="3">
-        <v>60140</v>
-      </c>
-      <c r="C436" s="3" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D436" s="3" t="s">
-        <v>1270</v>
-      </c>
-      <c r="E436" s="3" t="s">
-        <v>1271</v>
-      </c>
-      <c r="F436" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G436" s="3"/>
-      <c r="H436" s="3"/>
-    </row>
-    <row r="437" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A437" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B437" s="3">
-        <v>60187</v>
-      </c>
-      <c r="C437" s="3" t="s">
-        <v>1272</v>
-      </c>
-      <c r="D437" s="3" t="s">
-        <v>1273</v>
-      </c>
-      <c r="E437" s="3"/>
-      <c r="F437" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G437" s="3"/>
-      <c r="H437" s="3"/>
-    </row>
-    <row r="438" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A438" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B438" s="3">
-        <v>60272</v>
-      </c>
-      <c r="C438" s="3" t="s">
-        <v>1274</v>
-      </c>
-      <c r="D438" s="3" t="s">
-        <v>1275</v>
-      </c>
-      <c r="E438" s="3" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F438" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G438" s="3"/>
-      <c r="H438" s="3"/>
-    </row>
-    <row r="439" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A439" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B439" s="3">
-        <v>60293</v>
-      </c>
-      <c r="C439" s="3" t="s">
-        <v>1277</v>
-      </c>
-      <c r="D439" s="3" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E439" s="3" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F439" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G439" s="3"/>
-      <c r="H439" s="3"/>
-    </row>
-    <row r="440" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A440" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B440" s="3">
-        <v>60907</v>
-      </c>
-      <c r="C440" s="3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="D440" s="3" t="s">
-        <v>1239</v>
-      </c>
-      <c r="E440" s="3" t="s">
-        <v>1240</v>
-      </c>
-      <c r="F440" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G440" s="3"/>
-      <c r="H440" s="3"/>
-    </row>
-    <row r="441" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A441" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B441" s="3">
-        <v>62031</v>
-      </c>
-      <c r="C441" s="3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D441" s="3" t="s">
-        <v>1282</v>
-      </c>
-      <c r="E441" s="3"/>
-      <c r="F441" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G441" s="3"/>
-      <c r="H441" s="3"/>
-    </row>
-    <row r="442" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A442" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B442" s="3">
-        <v>62726</v>
-      </c>
-      <c r="C442" s="3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D442" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E442" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F442" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G442" s="3"/>
-      <c r="H442" s="3"/>
-    </row>
-    <row r="443" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A443" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B443" s="3">
-        <v>63330</v>
-      </c>
-      <c r="C443" s="3" t="s">
-        <v>1286</v>
-      </c>
-      <c r="D443" s="3" t="s">
-        <v>1287</v>
-      </c>
-      <c r="E443" s="3" t="s">
-        <v>1288</v>
-      </c>
-      <c r="F443" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G443" s="3"/>
-      <c r="H443" s="3"/>
-    </row>
-    <row r="444" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A444" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B444" s="3">
-        <v>64665</v>
-      </c>
-      <c r="C444" s="3" t="s">
-        <v>1289</v>
-      </c>
-      <c r="D444" s="3" t="s">
-        <v>1290</v>
-      </c>
-      <c r="E444" s="3" t="s">
-        <v>1291</v>
-      </c>
-      <c r="F444" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G444" s="3"/>
-      <c r="H444" s="3"/>
-    </row>
-    <row r="445" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A445" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B445" s="3">
-        <v>64893</v>
-      </c>
-      <c r="C445" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D445" s="3" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E445" s="3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="F445" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G445" s="3"/>
-      <c r="H445" s="3"/>
-    </row>
-    <row r="446" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A446" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B446" s="3">
-        <v>65785</v>
-      </c>
-      <c r="C446" s="3" t="s">
-        <v>1293</v>
-      </c>
-      <c r="D446" s="3" t="s">
-        <v>1294</v>
-      </c>
-      <c r="E446" s="3" t="s">
-        <v>1295</v>
-      </c>
-      <c r="F446" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G446" s="3"/>
-      <c r="H446" s="3"/>
-    </row>
-    <row r="447" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A447" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B447" s="3">
-        <v>65944</v>
-      </c>
-      <c r="C447" s="3" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D447" s="3" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E447" s="3" t="s">
-        <v>1251</v>
-      </c>
-      <c r="F447" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G447" s="3"/>
-      <c r="H447" s="3"/>
-    </row>
-    <row r="448" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A448" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B448" s="3">
-        <v>66534</v>
-      </c>
-      <c r="C448" s="3" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D448" s="3" t="s">
-        <v>1299</v>
-      </c>
-      <c r="E448" s="3" t="s">
-        <v>1300</v>
-      </c>
-      <c r="F448" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G448" s="3"/>
-      <c r="H448" s="3"/>
-    </row>
-    <row r="449" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A449" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B449" s="3">
-        <v>66964</v>
-      </c>
-      <c r="C449" s="3" t="s">
-        <v>1301</v>
-      </c>
-      <c r="D449" s="3" t="s">
-        <v>1302</v>
-      </c>
-      <c r="E449" s="3"/>
-      <c r="F449" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G449" s="3"/>
-      <c r="H449" s="3"/>
-    </row>
-    <row r="450" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A450" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B450" s="3">
-        <v>66989</v>
-      </c>
-      <c r="C450" s="3" t="s">
-        <v>1303</v>
-      </c>
-      <c r="D450" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E450" s="3" t="s">
-        <v>1304</v>
-      </c>
-      <c r="F450" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G450" s="3"/>
-      <c r="H450" s="3"/>
-    </row>
-    <row r="451" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A451" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B451" s="3">
-        <v>67022</v>
-      </c>
-      <c r="C451" s="3" t="s">
-        <v>1305</v>
-      </c>
-      <c r="D451" s="3" t="s">
-        <v>1306</v>
-      </c>
-      <c r="E451" s="3" t="s">
-        <v>1307</v>
-      </c>
-      <c r="F451" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G451" s="3"/>
-      <c r="H451" s="3"/>
-    </row>
-    <row r="452" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A452" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B452" s="3">
-        <v>67933</v>
-      </c>
-      <c r="C452" s="3" t="s">
-        <v>1308</v>
-      </c>
-      <c r="D452" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E452" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F452" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G452" s="3"/>
-      <c r="H452" s="3"/>
-    </row>
-    <row r="453" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A453" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B453" s="3">
-        <v>67984</v>
-      </c>
-      <c r="C453" s="3" t="s">
-        <v>1311</v>
-      </c>
-      <c r="D453" s="3" t="s">
-        <v>1312</v>
-      </c>
-      <c r="E453" s="3"/>
-      <c r="F453" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G453" s="3"/>
-      <c r="H453" s="3"/>
-    </row>
-    <row r="454" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A454" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B454" s="3">
-        <v>68048</v>
-      </c>
-      <c r="C454" s="3" t="s">
-        <v>1313</v>
-      </c>
-      <c r="D454" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E454" s="3" t="s">
-        <v>1314</v>
-      </c>
-      <c r="F454" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G454" s="3"/>
-      <c r="H454" s="3"/>
-    </row>
-    <row r="455" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A455" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B455" s="3">
-        <v>68506</v>
-      </c>
-      <c r="C455" s="3" t="s">
-        <v>1315</v>
-      </c>
-      <c r="D455" s="3" t="s">
-        <v>1309</v>
-      </c>
-      <c r="E455" s="3" t="s">
-        <v>1310</v>
-      </c>
-      <c r="F455" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G455" s="3"/>
-      <c r="H455" s="3"/>
-    </row>
-    <row r="456" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A456" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B456" s="3">
-        <v>69117</v>
-      </c>
-      <c r="C456" s="3" t="s">
-        <v>1316</v>
-      </c>
-      <c r="D456" s="3" t="s">
-        <v>1317</v>
-      </c>
-      <c r="E456" s="3" t="s">
-        <v>1318</v>
-      </c>
-      <c r="F456" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G456" s="3"/>
-      <c r="H456" s="3"/>
-    </row>
-    <row r="457" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A457" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B457" s="3">
-        <v>69304</v>
-      </c>
-      <c r="C457" s="3" t="s">
-        <v>1319</v>
-      </c>
-      <c r="D457" s="3" t="s">
-        <v>1320</v>
-      </c>
-      <c r="E457" s="3" t="s">
-        <v>1321</v>
-      </c>
-      <c r="F457" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G457" s="3"/>
-      <c r="H457" s="3"/>
-    </row>
-    <row r="458" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A458" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B458" s="3">
-        <v>70607</v>
-      </c>
-      <c r="C458" s="3" t="s">
-        <v>1322</v>
-      </c>
-      <c r="D458" s="3" t="s">
-        <v>1323</v>
-      </c>
-      <c r="E458" s="3" t="s">
-        <v>1324</v>
-      </c>
-      <c r="F458" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G458" s="3"/>
-      <c r="H458" s="3"/>
-    </row>
-    <row r="459" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A459" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B459" s="3">
-        <v>70859</v>
-      </c>
-      <c r="C459" s="3" t="s">
-        <v>1325</v>
-      </c>
-      <c r="D459" s="3" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E459" s="3" t="s">
-        <v>1327</v>
-      </c>
-      <c r="F459" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G459" s="3"/>
-      <c r="H459" s="3"/>
-    </row>
-    <row r="460" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A460" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B460" s="3">
-        <v>71202</v>
-      </c>
-      <c r="C460" s="3" t="s">
-        <v>1328</v>
-      </c>
-      <c r="D460" s="3" t="s">
-        <v>1329</v>
-      </c>
-      <c r="E460" s="3" t="s">
-        <v>1330</v>
-      </c>
-      <c r="F460" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G460" s="3"/>
-      <c r="H460" s="3"/>
-    </row>
-    <row r="461" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A461" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B461" s="3">
-        <v>71434</v>
-      </c>
-      <c r="C461" s="3" t="s">
-        <v>1331</v>
-      </c>
-      <c r="D461" s="3" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E461" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F461" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G461" s="3"/>
-      <c r="H461" s="3"/>
-    </row>
-    <row r="462" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A462" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B462" s="3">
-        <v>71506</v>
-      </c>
-      <c r="C462" s="3" t="s">
-        <v>1334</v>
-      </c>
-      <c r="D462" s="3" t="s">
-        <v>1335</v>
-      </c>
-      <c r="E462" s="3" t="s">
-        <v>1336</v>
-      </c>
-      <c r="F462" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G462" s="3"/>
-      <c r="H462" s="3"/>
-    </row>
-    <row r="463" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A463" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B463" s="3">
-        <v>71574</v>
-      </c>
-      <c r="C463" s="3" t="s">
-        <v>1337</v>
-      </c>
-      <c r="D463" s="3" t="s">
-        <v>1338</v>
-      </c>
-      <c r="E463" s="3"/>
-      <c r="F463" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G463" s="3"/>
-      <c r="H463" s="3"/>
-    </row>
-    <row r="464" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A464" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B464" s="3">
-        <v>71584</v>
-      </c>
-      <c r="C464" s="3" t="s">
-        <v>1292</v>
-      </c>
-      <c r="D464" s="3" t="s">
-        <v>1339</v>
-      </c>
-      <c r="E464" s="3" t="s">
-        <v>1340</v>
-      </c>
-      <c r="F464" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G464" s="3"/>
-      <c r="H464" s="3"/>
-    </row>
-    <row r="465" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A465" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B465" s="3">
-        <v>71722</v>
-      </c>
-      <c r="C465" s="3" t="s">
-        <v>1341</v>
-      </c>
-      <c r="D465" s="3" t="s">
-        <v>1342</v>
-      </c>
-      <c r="E465" s="3" t="s">
-        <v>1343</v>
-      </c>
-      <c r="F465" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G465" s="3"/>
-      <c r="H465" s="3"/>
-    </row>
-    <row r="466" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A466" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B466" s="3">
-        <v>71976</v>
-      </c>
-      <c r="C466" s="3" t="s">
-        <v>1344</v>
-      </c>
-      <c r="D466" s="3" t="s">
-        <v>1345</v>
-      </c>
-      <c r="E466" s="3"/>
-      <c r="F466" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G466" s="3"/>
-      <c r="H466" s="3"/>
-    </row>
-    <row r="467" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A467" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B467" s="3">
-        <v>72282</v>
-      </c>
-      <c r="C467" s="3" t="s">
-        <v>1346</v>
-      </c>
-      <c r="D467" s="3" t="s">
-        <v>1347</v>
-      </c>
-      <c r="E467" s="3" t="s">
-        <v>1348</v>
-      </c>
-      <c r="F467" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G467" s="3"/>
-      <c r="H467" s="3"/>
-    </row>
-    <row r="468" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A468" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B468" s="3">
-        <v>72504</v>
-      </c>
-      <c r="C468" s="3" t="s">
-        <v>1349</v>
-      </c>
-      <c r="D468" s="3" t="s">
-        <v>1350</v>
-      </c>
-      <c r="E468" s="3" t="s">
-        <v>1351</v>
-      </c>
-      <c r="F468" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G468" s="3"/>
-      <c r="H468" s="3"/>
-    </row>
-    <row r="469" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A469" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B469" s="3">
-        <v>72558</v>
-      </c>
-      <c r="C469" s="3" t="s">
-        <v>1352</v>
-      </c>
-      <c r="D469" s="3" t="s">
-        <v>1353</v>
-      </c>
-      <c r="E469" s="3"/>
-      <c r="F469" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G469" s="3"/>
-      <c r="H469" s="3"/>
-    </row>
-    <row r="470" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A470" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B470" s="3">
-        <v>73113</v>
-      </c>
-      <c r="C470" s="3" t="s">
-        <v>1354</v>
-      </c>
-      <c r="D470" s="3" t="s">
-        <v>1355</v>
-      </c>
-      <c r="E470" s="3" t="s">
-        <v>1356</v>
-      </c>
-      <c r="F470" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G470" s="3"/>
-      <c r="H470" s="3"/>
-    </row>
-    <row r="471" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A471" s="3" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B471" s="3">
-        <v>73400</v>
-      </c>
-      <c r="C471" s="3" t="s">
-        <v>1357</v>
-      </c>
-      <c r="D471" s="3" t="s">
-        <v>1358</v>
-      </c>
-      <c r="E471" s="3"/>
-      <c r="F471" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G471" s="3"/>
-      <c r="H471" s="3"/>
-    </row>
-    <row r="472" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A472" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B472" s="3">
-        <v>3097</v>
-      </c>
-      <c r="C472" s="3" t="s">
-        <v>1359</v>
-      </c>
-      <c r="D472" s="3"/>
-      <c r="E472" s="3"/>
-      <c r="F472" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G472" s="3"/>
-      <c r="H472" s="3"/>
-    </row>
-    <row r="473" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A473" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B473" s="3">
-        <v>8808</v>
-      </c>
-      <c r="C473" s="3" t="s">
-        <v>1360</v>
-      </c>
-      <c r="D473" s="3"/>
-      <c r="E473" s="3"/>
-      <c r="F473" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G473" s="3"/>
-      <c r="H473" s="3"/>
-    </row>
-    <row r="474" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A474" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B474" s="3">
-        <v>22360</v>
-      </c>
-      <c r="C474" s="3" t="s">
-        <v>1361</v>
-      </c>
-      <c r="D474" s="3"/>
-      <c r="E474" s="3"/>
-      <c r="F474" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G474" s="3"/>
-      <c r="H474" s="3"/>
-    </row>
-    <row r="475" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A475" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B475" s="3">
-        <v>24277</v>
-      </c>
-      <c r="C475" s="3" t="s">
-        <v>1362</v>
-      </c>
-      <c r="D475" s="3"/>
-      <c r="E475" s="3"/>
-      <c r="F475" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G475" s="3"/>
-      <c r="H475" s="3"/>
-    </row>
-    <row r="476" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A476" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B476" s="3">
-        <v>24578</v>
-      </c>
-      <c r="C476" s="3" t="s">
-        <v>1363</v>
-      </c>
-      <c r="D476" s="3"/>
-      <c r="E476" s="3"/>
-      <c r="F476" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G476" s="3"/>
-      <c r="H476" s="3"/>
-    </row>
-    <row r="477" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A477" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B477" s="3">
-        <v>27850</v>
-      </c>
-      <c r="C477" s="3" t="s">
-        <v>1364</v>
-      </c>
-      <c r="D477" s="3"/>
-      <c r="E477" s="3"/>
-      <c r="F477" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G477" s="3"/>
-      <c r="H477" s="3"/>
-    </row>
-    <row r="478" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A478" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B478" s="3">
-        <v>31516</v>
-      </c>
-      <c r="C478" s="3" t="s">
-        <v>1365</v>
-      </c>
-      <c r="D478" s="3"/>
-      <c r="E478" s="3"/>
-      <c r="F478" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G478" s="3"/>
-      <c r="H478" s="3"/>
-    </row>
-    <row r="479" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A479" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B479" s="3">
-        <v>31517</v>
-      </c>
-      <c r="C479" s="3" t="s">
-        <v>1366</v>
-      </c>
-      <c r="D479" s="3"/>
-      <c r="E479" s="3"/>
-      <c r="F479" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G479" s="3"/>
-      <c r="H479" s="3"/>
-    </row>
-    <row r="480" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A480" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B480" s="3">
-        <v>35054</v>
-      </c>
-      <c r="C480" s="3" t="s">
-        <v>1367</v>
-      </c>
-      <c r="D480" s="3"/>
-      <c r="E480" s="3"/>
-      <c r="F480" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G480" s="3"/>
-      <c r="H480" s="3"/>
-    </row>
-    <row r="481" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A481" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B481" s="3">
-        <v>37547</v>
-      </c>
-      <c r="C481" s="3" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D481" s="3"/>
-      <c r="E481" s="3"/>
-      <c r="F481" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G481" s="3"/>
-      <c r="H481" s="3"/>
-    </row>
-    <row r="482" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A482" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B482" s="3">
-        <v>40305</v>
-      </c>
-      <c r="C482" s="3" t="s">
-        <v>1369</v>
-      </c>
-      <c r="D482" s="3"/>
-      <c r="E482" s="3"/>
-      <c r="F482" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G482" s="3"/>
-      <c r="H482" s="3"/>
-    </row>
-    <row r="483" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A483" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B483" s="3">
-        <v>40815</v>
-      </c>
-      <c r="C483" s="3" t="s">
-        <v>1370</v>
-      </c>
-      <c r="D483" s="3"/>
-      <c r="E483" s="3"/>
-      <c r="F483" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G483" s="3"/>
-      <c r="H483" s="3"/>
-    </row>
-    <row r="484" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A484" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B484" s="3">
-        <v>46108</v>
-      </c>
-      <c r="C484" s="3" t="s">
-        <v>1371</v>
-      </c>
-      <c r="D484" s="3"/>
-      <c r="E484" s="3"/>
-      <c r="F484" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G484" s="3"/>
-      <c r="H484" s="3"/>
-    </row>
-    <row r="485" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A485" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B485" s="3">
-        <v>46455</v>
-      </c>
-      <c r="C485" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="D485" s="3"/>
-      <c r="E485" s="3"/>
-      <c r="F485" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G485" s="3"/>
-      <c r="H485" s="3"/>
-    </row>
-    <row r="486" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A486" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B486" s="3">
-        <v>46458</v>
-      </c>
-      <c r="C486" s="3" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D486" s="3"/>
-      <c r="E486" s="3"/>
-      <c r="F486" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G486" s="3"/>
-      <c r="H486" s="3"/>
-    </row>
-    <row r="487" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A487" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B487" s="3">
-        <v>52367</v>
-      </c>
-      <c r="C487" s="3" t="s">
-        <v>1374</v>
-      </c>
-      <c r="D487" s="3"/>
-      <c r="E487" s="3"/>
-      <c r="F487" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G487" s="3"/>
-      <c r="H487" s="3"/>
-    </row>
-    <row r="488" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A488" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B488" s="3">
-        <v>53732</v>
-      </c>
-      <c r="C488" s="3" t="s">
-        <v>1375</v>
-      </c>
-      <c r="D488" s="3"/>
-      <c r="E488" s="3"/>
-      <c r="F488" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G488" s="3"/>
-      <c r="H488" s="3"/>
-    </row>
-    <row r="489" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A489" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B489" s="3">
-        <v>53738</v>
-      </c>
-      <c r="C489" s="3" t="s">
-        <v>1376</v>
-      </c>
-      <c r="D489" s="3"/>
-      <c r="E489" s="3"/>
-      <c r="F489" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G489" s="3"/>
-      <c r="H489" s="3"/>
-    </row>
-    <row r="490" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A490" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B490" s="3">
-        <v>55212</v>
-      </c>
-      <c r="C490" s="3" t="s">
-        <v>1377</v>
-      </c>
-      <c r="D490" s="3"/>
-      <c r="E490" s="3"/>
-      <c r="F490" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G490" s="3"/>
-      <c r="H490" s="3"/>
-    </row>
-    <row r="491" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A491" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B491" s="3">
-        <v>55755</v>
-      </c>
-      <c r="C491" s="3" t="s">
-        <v>1378</v>
-      </c>
-      <c r="D491" s="3"/>
-      <c r="E491" s="3"/>
-      <c r="F491" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G491" s="3"/>
-      <c r="H491" s="3"/>
-    </row>
-    <row r="492" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A492" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B492" s="3">
-        <v>56353</v>
-      </c>
-      <c r="C492" s="3" t="s">
-        <v>1379</v>
-      </c>
-      <c r="D492" s="3"/>
-      <c r="E492" s="3"/>
-      <c r="F492" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G492" s="3"/>
-      <c r="H492" s="3"/>
-    </row>
-    <row r="493" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A493" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B493" s="3">
-        <v>56532</v>
-      </c>
-      <c r="C493" s="3" t="s">
-        <v>1380</v>
-      </c>
-      <c r="D493" s="3"/>
-      <c r="E493" s="3"/>
-      <c r="F493" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G493" s="3"/>
-      <c r="H493" s="3"/>
-    </row>
-    <row r="494" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A494" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B494" s="3">
-        <v>58900</v>
-      </c>
-      <c r="C494" s="3" t="s">
-        <v>1381</v>
-      </c>
-      <c r="D494" s="3"/>
-      <c r="E494" s="3"/>
-      <c r="F494" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G494" s="3"/>
-      <c r="H494" s="3"/>
-    </row>
-    <row r="495" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A495" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B495" s="3">
-        <v>59752</v>
-      </c>
-      <c r="C495" s="3" t="s">
-        <v>1382</v>
-      </c>
-      <c r="D495" s="3"/>
-      <c r="E495" s="3"/>
-      <c r="F495" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G495" s="3"/>
-      <c r="H495" s="3"/>
-    </row>
-    <row r="496" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A496" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B496" s="3">
-        <v>59971</v>
-      </c>
-      <c r="C496" s="3" t="s">
-        <v>1383</v>
-      </c>
-      <c r="D496" s="3"/>
-      <c r="E496" s="3"/>
-      <c r="F496" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G496" s="3"/>
-      <c r="H496" s="3"/>
-    </row>
-    <row r="497" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A497" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B497" s="3">
-        <v>60386</v>
-      </c>
-      <c r="C497" s="3" t="s">
-        <v>1384</v>
-      </c>
-      <c r="D497" s="3"/>
-      <c r="E497" s="3"/>
-      <c r="F497" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G497" s="3"/>
-      <c r="H497" s="3"/>
-    </row>
-    <row r="498" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A498" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B498" s="3">
-        <v>60463</v>
-      </c>
-      <c r="C498" s="3" t="s">
-        <v>1385</v>
-      </c>
-      <c r="D498" s="3"/>
-      <c r="E498" s="3"/>
-      <c r="F498" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G498" s="3"/>
-      <c r="H498" s="3"/>
-    </row>
-    <row r="499" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A499" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B499" s="3">
-        <v>60627</v>
-      </c>
-      <c r="C499" s="3" t="s">
-        <v>1386</v>
-      </c>
-      <c r="D499" s="3"/>
-      <c r="E499" s="3"/>
-      <c r="F499" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G499" s="3"/>
-      <c r="H499" s="3"/>
-    </row>
-    <row r="500" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A500" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B500" s="3">
-        <v>60769</v>
-      </c>
-      <c r="C500" s="3" t="s">
-        <v>1387</v>
-      </c>
-      <c r="D500" s="3"/>
-      <c r="E500" s="3"/>
-      <c r="F500" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G500" s="3"/>
-      <c r="H500" s="3"/>
-    </row>
-    <row r="501" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A501" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B501" s="3">
-        <v>60911</v>
-      </c>
-      <c r="C501" s="3" t="s">
-        <v>1388</v>
-      </c>
-      <c r="D501" s="3"/>
-      <c r="E501" s="3"/>
-      <c r="F501" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G501" s="3"/>
-      <c r="H501" s="3"/>
-    </row>
-    <row r="502" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A502" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B502" s="3">
-        <v>61208</v>
-      </c>
-      <c r="C502" s="3" t="s">
-        <v>1389</v>
-      </c>
-      <c r="D502" s="3"/>
-      <c r="E502" s="3"/>
-      <c r="F502" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G502" s="3"/>
-      <c r="H502" s="3"/>
-    </row>
-    <row r="503" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A503" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B503" s="3">
-        <v>62583</v>
-      </c>
-      <c r="C503" s="3" t="s">
-        <v>1390</v>
-      </c>
-      <c r="D503" s="3"/>
-      <c r="E503" s="3"/>
-      <c r="F503" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G503" s="3"/>
-      <c r="H503" s="3"/>
-    </row>
-    <row r="504" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A504" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B504" s="3">
-        <v>63140</v>
-      </c>
-      <c r="C504" s="3" t="s">
-        <v>1391</v>
-      </c>
-      <c r="D504" s="3"/>
-      <c r="E504" s="3"/>
-      <c r="F504" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G504" s="3"/>
-      <c r="H504" s="3"/>
-    </row>
-    <row r="505" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A505" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B505" s="3">
-        <v>63141</v>
-      </c>
-      <c r="C505" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="D505" s="3"/>
-      <c r="E505" s="3"/>
-      <c r="F505" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G505" s="3"/>
-      <c r="H505" s="3"/>
-    </row>
-    <row r="506" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A506" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B506" s="3">
-        <v>63326</v>
-      </c>
-      <c r="C506" s="3" t="s">
-        <v>1393</v>
-      </c>
-      <c r="D506" s="3"/>
-      <c r="E506" s="3"/>
-      <c r="F506" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G506" s="3"/>
-      <c r="H506" s="3"/>
-    </row>
-    <row r="507" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A507" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B507" s="3">
-        <v>63622</v>
-      </c>
-      <c r="C507" s="3" t="s">
-        <v>1394</v>
-      </c>
-      <c r="D507" s="3"/>
-      <c r="E507" s="3"/>
-      <c r="F507" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G507" s="3"/>
-      <c r="H507" s="3"/>
-    </row>
-    <row r="508" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A508" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B508" s="3">
-        <v>65135</v>
-      </c>
-      <c r="C508" s="3" t="s">
-        <v>1395</v>
-      </c>
-      <c r="D508" s="3"/>
-      <c r="E508" s="3"/>
-      <c r="F508" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G508" s="3"/>
-      <c r="H508" s="3"/>
-    </row>
-    <row r="509" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A509" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B509" s="3">
-        <v>65394</v>
-      </c>
-      <c r="C509" s="3" t="s">
-        <v>1396</v>
-      </c>
-      <c r="D509" s="3"/>
-      <c r="E509" s="3"/>
-      <c r="F509" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G509" s="3"/>
-      <c r="H509" s="3"/>
-    </row>
-    <row r="510" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A510" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B510" s="3">
-        <v>65427</v>
-      </c>
-      <c r="C510" s="3" t="s">
-        <v>1397</v>
-      </c>
-      <c r="D510" s="3"/>
-      <c r="E510" s="3"/>
-      <c r="F510" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G510" s="3"/>
-      <c r="H510" s="3"/>
-    </row>
-    <row r="511" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A511" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B511" s="3">
-        <v>65554</v>
-      </c>
-      <c r="C511" s="3" t="s">
-        <v>1398</v>
-      </c>
-      <c r="D511" s="3"/>
-      <c r="E511" s="3"/>
-      <c r="F511" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G511" s="3"/>
-      <c r="H511" s="3"/>
-    </row>
-    <row r="512" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A512" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B512" s="3">
-        <v>65737</v>
-      </c>
-      <c r="C512" s="3" t="s">
-        <v>1399</v>
-      </c>
-      <c r="D512" s="3"/>
-      <c r="E512" s="3"/>
-      <c r="F512" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G512" s="3"/>
-      <c r="H512" s="3"/>
-    </row>
-    <row r="513" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A513" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B513" s="3">
-        <v>66485</v>
-      </c>
-      <c r="C513" s="3" t="s">
-        <v>1400</v>
-      </c>
-      <c r="D513" s="3"/>
-      <c r="E513" s="3"/>
-      <c r="F513" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G513" s="3"/>
-      <c r="H513" s="3"/>
-    </row>
-    <row r="514" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A514" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B514" s="3">
-        <v>67083</v>
-      </c>
-      <c r="C514" s="3" t="s">
-        <v>1401</v>
-      </c>
-      <c r="D514" s="3"/>
-      <c r="E514" s="3"/>
-      <c r="F514" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G514" s="3"/>
-      <c r="H514" s="3"/>
-    </row>
-    <row r="515" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A515" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B515" s="3">
-        <v>67978</v>
-      </c>
-      <c r="C515" s="3" t="s">
-        <v>1402</v>
-      </c>
-      <c r="D515" s="3"/>
-      <c r="E515" s="3"/>
-      <c r="F515" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G515" s="3"/>
-      <c r="H515" s="3"/>
-    </row>
-    <row r="516" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A516" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B516" s="3">
-        <v>68236</v>
-      </c>
-      <c r="C516" s="3" t="s">
-        <v>1403</v>
-      </c>
-      <c r="D516" s="3"/>
-      <c r="E516" s="3"/>
-      <c r="F516" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G516" s="3"/>
-      <c r="H516" s="3"/>
-    </row>
-    <row r="517" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A517" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B517" s="3">
-        <v>70505</v>
-      </c>
-      <c r="C517" s="3" t="s">
-        <v>1404</v>
-      </c>
-      <c r="D517" s="3"/>
-      <c r="E517" s="3"/>
-      <c r="F517" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G517" s="3"/>
-      <c r="H517" s="3"/>
-    </row>
-    <row r="518" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A518" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B518" s="3">
-        <v>70646</v>
-      </c>
-      <c r="C518" s="3" t="s">
-        <v>1405</v>
-      </c>
-      <c r="D518" s="3"/>
-      <c r="E518" s="3"/>
-      <c r="F518" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G518" s="3"/>
-      <c r="H518" s="3"/>
-    </row>
-    <row r="519" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A519" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B519" s="3">
-        <v>70668</v>
-      </c>
-      <c r="C519" s="3" t="s">
-        <v>1406</v>
-      </c>
-      <c r="D519" s="3"/>
-      <c r="E519" s="3"/>
-      <c r="F519" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G519" s="3"/>
-      <c r="H519" s="3"/>
-    </row>
-    <row r="520" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A520" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B520" s="3">
-        <v>70799</v>
-      </c>
-      <c r="C520" s="3" t="s">
-        <v>1407</v>
-      </c>
-      <c r="D520" s="3"/>
-      <c r="E520" s="3"/>
-      <c r="F520" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G520" s="3"/>
-      <c r="H520" s="3"/>
-    </row>
-    <row r="521" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A521" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B521" s="3">
-        <v>70996</v>
-      </c>
-      <c r="C521" s="3" t="s">
-        <v>1408</v>
-      </c>
-      <c r="D521" s="3"/>
-      <c r="E521" s="3"/>
-      <c r="F521" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G521" s="3"/>
-      <c r="H521" s="3"/>
-    </row>
-    <row r="522" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A522" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B522" s="3">
-        <v>71453</v>
-      </c>
-      <c r="C522" s="3" t="s">
-        <v>1409</v>
-      </c>
-      <c r="D522" s="3"/>
-      <c r="E522" s="3"/>
-      <c r="F522" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G522" s="3"/>
-      <c r="H522" s="3"/>
-    </row>
-    <row r="523" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A523" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B523" s="3">
-        <v>71532</v>
-      </c>
-      <c r="C523" s="3" t="s">
-        <v>1410</v>
-      </c>
-      <c r="D523" s="3"/>
-      <c r="E523" s="3"/>
-      <c r="F523" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G523" s="3"/>
-      <c r="H523" s="3"/>
-    </row>
-    <row r="524" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A524" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B524" s="3">
-        <v>71710</v>
-      </c>
-      <c r="C524" s="3" t="s">
-        <v>1411</v>
-      </c>
-      <c r="D524" s="3"/>
-      <c r="E524" s="3"/>
-      <c r="F524" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G524" s="3"/>
-      <c r="H524" s="3"/>
-    </row>
-    <row r="525" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A525" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B525" s="3">
-        <v>71724</v>
-      </c>
-      <c r="C525" s="3" t="s">
-        <v>1412</v>
-      </c>
-      <c r="D525" s="3"/>
-      <c r="E525" s="3"/>
-      <c r="F525" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G525" s="3"/>
-      <c r="H525" s="3"/>
-    </row>
-    <row r="526" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A526" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B526" s="3">
-        <v>71791</v>
-      </c>
-      <c r="C526" s="3" t="s">
-        <v>1413</v>
-      </c>
-      <c r="D526" s="3"/>
-      <c r="E526" s="3"/>
-      <c r="F526" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G526" s="3"/>
-      <c r="H526" s="3"/>
-    </row>
-    <row r="527" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A527" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B527" s="3">
-        <v>71838</v>
-      </c>
-      <c r="C527" s="3" t="s">
-        <v>1414</v>
-      </c>
-      <c r="D527" s="3"/>
-      <c r="E527" s="3"/>
-      <c r="F527" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G527" s="3"/>
-      <c r="H527" s="3"/>
-    </row>
-    <row r="528" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A528" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B528" s="3">
-        <v>71844</v>
-      </c>
-      <c r="C528" s="3" t="s">
-        <v>1415</v>
-      </c>
-      <c r="D528" s="3"/>
-      <c r="E528" s="3"/>
-      <c r="F528" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G528" s="3"/>
-      <c r="H528" s="3"/>
-    </row>
-    <row r="529" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A529" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B529" s="3">
-        <v>72103</v>
-      </c>
-      <c r="C529" s="3" t="s">
-        <v>1416</v>
-      </c>
-      <c r="D529" s="3"/>
-      <c r="E529" s="3"/>
-      <c r="F529" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G529" s="3"/>
-      <c r="H529" s="3"/>
-    </row>
-    <row r="530" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A530" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B530" s="3">
-        <v>72774</v>
-      </c>
-      <c r="C530" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="D530" s="3"/>
-      <c r="E530" s="3"/>
-      <c r="F530" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G530" s="3"/>
-      <c r="H530" s="3"/>
-    </row>
-    <row r="531" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A531" s="3" t="s">
-        <v>1219</v>
-      </c>
-      <c r="B531" s="3">
-        <v>73355</v>
-      </c>
-      <c r="C531" s="3" t="s">
-        <v>1418</v>
-      </c>
-      <c r="D531" s="3"/>
-      <c r="E531" s="3"/>
-      <c r="F531" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="G531" s="3"/>
-      <c r="H531" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22444,7 +19524,7 @@
         <v>122</v>
       </c>
       <c r="C2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -22482,7 +19562,7 @@
         <v>126</v>
       </c>
       <c r="C3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -22520,7 +19600,7 @@
         <v>130</v>
       </c>
       <c r="C4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -22558,7 +19638,7 @@
         <v>134</v>
       </c>
       <c r="C5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -22616,12 +19696,6 @@
       <c r="I6" t="s">
         <v>141</v>
       </c>
-      <c r="J6" t="s">
-        <v>111</v>
-      </c>
-      <c r="K6" t="s">
-        <v>111</v>
-      </c>
       <c r="L6" t="s">
         <v>111</v>
       </c>
@@ -22634,7 +19708,7 @@
         <v>142</v>
       </c>
       <c r="C7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -22672,7 +19746,7 @@
         <v>149</v>
       </c>
       <c r="C8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -22705,7 +19779,7 @@
         <v>150</v>
       </c>
       <c r="C9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -22738,7 +19812,7 @@
         <v>151</v>
       </c>
       <c r="C10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -22771,7 +19845,7 @@
         <v>161</v>
       </c>
       <c r="C11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11">
         <v>0</v>
